--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92527303348</v>
+        <v>46157.93095896202</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93095896202</v>
+        <v>46157.93356726523</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93356726523</v>
+        <v>46157.93651546055</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93651546055</v>
+        <v>46158.28184713401</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28184713401</v>
+        <v>46158.29762996465</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29762996465</v>
+        <v>46158.29778851486</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29778851486</v>
+        <v>46158.33346138663</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33346138663</v>
+        <v>46158.37204888849</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.0_ЭЦП/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37204888849</v>
+        <v>46158.37400722205</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
